--- a/强基查证清单_官方核对.xlsx
+++ b/强基查证清单_官方核对.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>初试6月19日左右；复试6月10日</t>
+          <t>初试6月19日左右；复试6月21日左右</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6月11日</t>
+          <t>考试确认5月31日-6月11日12:00；考核时间另行公告</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>初试4月10日；复试4月10日</t>
+          <t>初试6月12日左右；复试6月18日左右</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
